--- a/data/raw/inventory/Week 35/Tonor/Imports (OrderPilot).xlsx
+++ b/data/raw/inventory/Week 35/Tonor/Imports (OrderPilot).xlsx
@@ -1638,7 +1638,7 @@
         <v>80</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="F41" t="s">
         <v>108</v>
@@ -2167,7 +2167,7 @@
         <v>103</v>
       </c>
       <c r="E64">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F64" t="s">
         <v>108</v>
